--- a/_102_Character.xlsx
+++ b/_102_Character.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7AC20A-1544-4D2E-954C-DCC3055F8961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC166FA-36F7-451C-BE4C-0B94F28B71BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -150,11 +150,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rarity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>double</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EGrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +603,7 @@
         <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
@@ -661,58 +677,58 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>2</v>
@@ -734,8 +750,8 @@
       <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2">
-        <v>1</v>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="E4" s="2">
         <v>150</v>
@@ -808,8 +824,8 @@
       <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="3">
-        <v>2</v>
+      <c r="D5" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="E5" s="3">
         <v>140</v>
@@ -882,8 +898,8 @@
       <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2">
-        <v>3</v>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E6" s="2">
         <v>130</v>
